--- a/Savets 2026/admin/output/Group Scorecards.xlsx
+++ b/Savets 2026/admin/output/Group Scorecards.xlsx
@@ -45,7 +45,7 @@
     <t>TABLE:</t>
   </si>
   <si>
-    <t>RAVENS 2026 TERRENCE ORR CHAMPIONSHIP</t>
+    <t>SAVETTS 2026</t>
   </si>
   <si>
     <t>EVENT:</t>
